--- a/weeklyNew/221019_A2U 원격 주장비(SGW) 설치현황 List(인프라구축센터).xlsx
+++ b/weeklyNew/221019_A2U 원격 주장비(SGW) 설치현황 List(인프라구축센터).xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20387"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20391"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023\_Pi2Work\weeklyNew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F99F30-08A0-4EFD-819D-6D9148EC2725}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A497C810-CF4A-485E-8E01-74F2C4411B50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="-105" windowWidth="19395" windowHeight="12195" xr2:uid="{19E6D41C-4C47-4920-82CF-2B5DA9211324}"/>
+    <workbookView xWindow="19110" yWindow="-105" windowWidth="19395" windowHeight="12195" activeTab="1" xr2:uid="{19E6D41C-4C47-4920-82CF-2B5DA9211324}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$4:$L$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -129,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>구분/년도</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -186,6 +190,31 @@
     <t>원격기동(효율관리포함)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>A2U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIMON</t>
+  </si>
+  <si>
+    <t>KISAN</t>
+  </si>
+  <si>
+    <t>LGCNS</t>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업체구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>■ 원격통신장비(SGW) 설치 수량 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -193,9 +222,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0&quot; EA&quot;"/>
+    <numFmt numFmtId="177" formatCode="#,##0&quot; EA&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +283,32 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -287,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -544,13 +599,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -590,6 +734,30 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -605,28 +773,46 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -955,14 +1141,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="19">
+      <c r="L2" s="20">
         <v>44853</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="18"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="13"/>
     </row>
     <row r="3" spans="2:14" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G3" s="2"/>
@@ -1006,7 +1192,7 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="16.899999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="25" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1045,44 +1231,44 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="14">
         <v>2</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="14">
         <v>1</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="14">
         <v>5</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="14">
         <v>0</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="14">
         <v>19</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="14">
         <v>12</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="14">
         <v>60</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="14">
         <v>57</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="14">
         <v>67</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="16">
         <f t="shared" ref="M6:M16" si="0">SUM(D6:L6)</f>
         <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1119,42 +1305,42 @@
       </c>
     </row>
     <row r="8" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="13"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14">
         <v>20</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="14">
         <v>0</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="14">
         <v>6</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="14">
         <v>5</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="14">
         <v>10</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="14">
         <v>4</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="14">
         <v>5</v>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="14">
         <v>2</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="16">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1185,30 +1371,30 @@
       </c>
     </row>
     <row r="10" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="13"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14">
         <v>19</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="14">
         <v>2</v>
       </c>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="22">
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="16">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1235,32 +1421,32 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="13"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14">
         <v>17</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="14">
         <v>9</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="14">
         <v>12</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="22">
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="16">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -1285,30 +1471,30 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="13"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14">
         <v>110</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="14">
         <v>17</v>
       </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="22">
+      <c r="L14" s="14"/>
+      <c r="M14" s="16">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -1339,36 +1525,36 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="13"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20">
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14">
         <v>44</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="14">
         <v>95</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="14">
         <v>88</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="14">
         <v>76</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="14">
         <v>3</v>
       </c>
-      <c r="L16" s="20"/>
-      <c r="M16" s="22">
+      <c r="L16" s="14"/>
+      <c r="M16" s="16">
         <f t="shared" si="0"/>
         <v>306</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="21" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -1399,41 +1585,41 @@
       </c>
     </row>
     <row r="18" spans="2:13" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="14"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21">
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15">
         <v>179</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="15">
         <v>60</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="15">
         <v>51</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="15">
         <v>41</v>
       </c>
-      <c r="L18" s="21">
+      <c r="L18" s="15">
         <v>48</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="17">
         <f t="shared" si="1"/>
         <v>379</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:13" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="24">
+      <c r="L20" s="24"/>
+      <c r="M20" s="18">
         <f>M6+M8+M10+M12+M14+M16+M18</f>
         <v>1146</v>
       </c>
@@ -1455,4 +1641,454 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669CD544-1084-4CE4-BF3C-414FAA2301F0}">
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.25" style="26" customWidth="1"/>
+    <col min="2" max="2" width="14.625" style="26" customWidth="1"/>
+    <col min="3" max="11" width="10.25" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" style="26" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+    </row>
+    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="27">
+        <v>2014</v>
+      </c>
+      <c r="D4" s="27">
+        <v>2015</v>
+      </c>
+      <c r="E4" s="27">
+        <v>2016</v>
+      </c>
+      <c r="F4" s="27">
+        <v>2017</v>
+      </c>
+      <c r="G4" s="27">
+        <v>2018</v>
+      </c>
+      <c r="H4" s="27">
+        <v>2019</v>
+      </c>
+      <c r="I4" s="27">
+        <v>2020</v>
+      </c>
+      <c r="J4" s="27">
+        <v>2021</v>
+      </c>
+      <c r="K4" s="27">
+        <v>2022</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="34">
+        <v>4</v>
+      </c>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="35">
+        <f t="shared" ref="L5:L7" si="0">SUM(C5:K5)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="36"/>
+      <c r="B6" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="34">
+        <v>2</v>
+      </c>
+      <c r="D6" s="34">
+        <v>50</v>
+      </c>
+      <c r="E6" s="34">
+        <v>46</v>
+      </c>
+      <c r="F6" s="34">
+        <v>18</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="35">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34">
+        <v>27</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="35">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
+      <c r="B8" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="38">
+        <v>2</v>
+      </c>
+      <c r="D8" s="38">
+        <v>1</v>
+      </c>
+      <c r="E8" s="38">
+        <v>5</v>
+      </c>
+      <c r="F8" s="38">
+        <v>0</v>
+      </c>
+      <c r="G8" s="38">
+        <v>19</v>
+      </c>
+      <c r="H8" s="38">
+        <v>12</v>
+      </c>
+      <c r="I8" s="38">
+        <v>60</v>
+      </c>
+      <c r="J8" s="38">
+        <v>57</v>
+      </c>
+      <c r="K8" s="38">
+        <v>67</v>
+      </c>
+      <c r="L8" s="35">
+        <f>SUM(C8:K8)</f>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38">
+        <v>20</v>
+      </c>
+      <c r="E9" s="38">
+        <v>0</v>
+      </c>
+      <c r="F9" s="38">
+        <v>6</v>
+      </c>
+      <c r="G9" s="38">
+        <v>5</v>
+      </c>
+      <c r="H9" s="38">
+        <v>10</v>
+      </c>
+      <c r="I9" s="38">
+        <v>4</v>
+      </c>
+      <c r="J9" s="38">
+        <v>5</v>
+      </c>
+      <c r="K9" s="38">
+        <v>2</v>
+      </c>
+      <c r="L9" s="35">
+        <f>SUM(C9:K9)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38">
+        <v>19</v>
+      </c>
+      <c r="H10" s="38">
+        <v>2</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="35">
+        <f>SUM(C10:K10)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38">
+        <v>17</v>
+      </c>
+      <c r="H11" s="38">
+        <v>9</v>
+      </c>
+      <c r="I11" s="38">
+        <v>12</v>
+      </c>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="35">
+        <f>SUM(C11:K11)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38">
+        <v>110</v>
+      </c>
+      <c r="J12" s="38">
+        <v>17</v>
+      </c>
+      <c r="K12" s="38"/>
+      <c r="L12" s="35">
+        <f>SUM(C12:K12)</f>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38">
+        <v>44</v>
+      </c>
+      <c r="G13" s="38">
+        <v>95</v>
+      </c>
+      <c r="H13" s="38">
+        <v>88</v>
+      </c>
+      <c r="I13" s="38">
+        <v>76</v>
+      </c>
+      <c r="J13" s="38">
+        <v>3</v>
+      </c>
+      <c r="K13" s="38"/>
+      <c r="L13" s="35">
+        <f>SUM(C13:K13)</f>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38">
+        <v>179</v>
+      </c>
+      <c r="H14" s="38">
+        <v>60</v>
+      </c>
+      <c r="I14" s="38">
+        <v>51</v>
+      </c>
+      <c r="J14" s="38">
+        <v>41</v>
+      </c>
+      <c r="K14" s="38">
+        <v>48</v>
+      </c>
+      <c r="L14" s="35">
+        <f>SUM(C14:K14)</f>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="39">
+        <f>SUM(L5:L14)</f>
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L14" xr:uid="{E398F224-C312-4600-BD87-6727DFE94768}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A15:K15"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>